--- a/data/trans_dic/P1805_2016_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1805_2016_2023-Provincia-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 6,9</t>
+          <t>1,81; 6,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,78</t>
+          <t>0,0; 2,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,38; 10,96</t>
+          <t>4,7; 11,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,63</t>
+          <t>1,52; 4,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,73; 7,71</t>
+          <t>3,76; 7,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,04</t>
+          <t>1,06; 2,97</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 7,34</t>
+          <t>2,28; 6,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,27</t>
+          <t>0,38; 2,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 6,17</t>
+          <t>2,67; 6,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,52</t>
+          <t>0,38; 1,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,7</t>
+          <t>2,7; 5,38</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,95</t>
+          <t>0,6; 3,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,59</t>
+          <t>1,63; 6,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 7,47</t>
+          <t>2,44; 7,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 7,8</t>
+          <t>3,81; 7,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,76</t>
+          <t>1,84; 4,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,05; 6,07</t>
+          <t>3,13; 6,03</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,57</t>
+          <t>1,27; 4,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,84; 10,71</t>
+          <t>3,29; 9,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,34</t>
+          <t>1,79; 5,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,92</t>
+          <t>3,84; 8,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,26</t>
+          <t>1,81; 4,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 7,49</t>
+          <t>4,24; 7,93</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,58</t>
+          <t>1,2; 6,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,25</t>
+          <t>0,44; 3,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,11</t>
+          <t>0,65; 2,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,09</t>
+          <t>1,12; 4,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,27</t>
+          <t>0,58; 2,08</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,99</t>
+          <t>0,0; 2,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,53</t>
+          <t>1,29; 4,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,96; 6,64</t>
+          <t>1,91; 6,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,29</t>
+          <t>2,03; 5,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,34</t>
+          <t>1,36; 4,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,16</t>
+          <t>2,07; 4,29</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,99</t>
+          <t>0,36; 2,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,09; 7,69</t>
+          <t>3,03; 7,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,14</t>
+          <t>2,07; 5,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 7,65</t>
+          <t>4,82; 8,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,23</t>
+          <t>1,47; 3,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,35; 6,98</t>
+          <t>4,43; 7,2</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,6</t>
+          <t>1,47; 3,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,19</t>
+          <t>1,48; 3,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,22; 6,5</t>
+          <t>3,24; 6,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,74</t>
+          <t>1,75; 3,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,63; 4,58</t>
+          <t>2,66; 4,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,98</t>
+          <t>1,9; 3,34</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,28</t>
+          <t>1,39; 2,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,09</t>
+          <t>2,61; 4,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,1; 4,54</t>
+          <t>3,07; 4,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,12; 4,66</t>
+          <t>3,62; 4,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,41; 3,22</t>
+          <t>2,37; 3,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,1; 4,17</t>
+          <t>3,31; 4,26</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7734</t>
+          <t>8212</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11357</t>
         </is>
       </c>
     </row>
@@ -1506,32 +1506,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5324; 20260</t>
+          <t>5317; 19454</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1003; 11774</t>
+          <t>0; 7960</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12654; 31653</t>
+          <t>13557; 32483</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4550; 13420</t>
+          <t>4820; 13097</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21731; 44931</t>
+          <t>21925; 46095</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6738; 18280</t>
+          <t>6714; 18861</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>20484</t>
+          <t>19860</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20973</t>
+          <t>21269</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41457</t>
+          <t>41129</t>
         </is>
       </c>
     </row>
@@ -1624,32 +1624,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7157</t>
+          <t>0; 6605</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11586; 38029</t>
+          <t>12100; 35817</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2052; 11871</t>
+          <t>1982; 12245</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12926; 31712</t>
+          <t>14553; 34434</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3964; 15556</t>
+          <t>3913; 15094</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29215; 58830</t>
+          <t>29078; 57887</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9380</t>
+          <t>10526</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18993</t>
+          <t>19177</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28373</t>
+          <t>29703</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2206; 12593</t>
+          <t>1923; 11331</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4817; 17662</t>
+          <t>5161; 19826</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8505; 25129</t>
+          <t>8219; 24924</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13342; 27227</t>
+          <t>13576; 28017</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11885; 31187</t>
+          <t>12069; 31668</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20297; 40381</t>
+          <t>21015; 40519</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>20469</t>
+          <t>21524</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21690</t>
+          <t>24601</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42159</t>
+          <t>46125</t>
         </is>
       </c>
     </row>
@@ -1860,32 +1860,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4699; 16911</t>
+          <t>4699; 17233</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11991; 33477</t>
+          <t>12278; 34296</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6347; 20675</t>
+          <t>6936; 21864</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11823; 32920</t>
+          <t>16188; 35548</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13898; 32292</t>
+          <t>13729; 32694</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27774; 59064</t>
+          <t>33675; 63051</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4854</t>
         </is>
       </c>
     </row>
@@ -1978,32 +1978,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2814; 13903</t>
+          <t>2537; 13387</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4290</t>
+          <t>0; 5057</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>959; 9293</t>
+          <t>957; 8683</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1577; 6485</t>
+          <t>1487; 6692</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5423; 17579</t>
+          <t>4829; 18057</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2390; 8797</t>
+          <t>2490; 9020</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8630</t>
+          <t>9241</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15682</t>
+          <t>15995</t>
         </is>
       </c>
     </row>
@@ -2096,32 +2096,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>977; 7868</t>
+          <t>0; 7518</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3425; 12203</t>
+          <t>3484; 12741</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5345; 18137</t>
+          <t>5230; 18148</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5246; 13610</t>
+          <t>5358; 14638</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7321; 23299</t>
+          <t>7305; 22426</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10270; 21911</t>
+          <t>11081; 22939</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>31240</t>
+          <t>34213</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45028</t>
+          <t>49891</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76268</t>
+          <t>84104</t>
         </is>
       </c>
     </row>
@@ -2214,32 +2214,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2291; 13084</t>
+          <t>2377; 13901</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>19288; 48038</t>
+          <t>21824; 54125</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14572; 35532</t>
+          <t>14290; 36785</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18706; 64977</t>
+          <t>37228; 67053</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>19779; 43511</t>
+          <t>19866; 42458</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>49400; 102823</t>
+          <t>66111; 107360</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>19656</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18524</t>
+          <t>21434</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35766</t>
+          <t>41091</t>
         </is>
       </c>
     </row>
@@ -2332,32 +2332,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>10826; 28061</t>
+          <t>11427; 27634</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>6680; 29636</t>
+          <t>11825; 29853</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>26637; 53662</t>
+          <t>26749; 53404</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12800; 26839</t>
+          <t>14583; 31106</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>42175; 73425</t>
+          <t>42722; 73133</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>21468; 49114</t>
+          <t>30965; 54412</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>110924</t>
+          <t>117165</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>144810</t>
+          <t>157192</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>255734</t>
+          <t>274357</t>
         </is>
       </c>
     </row>
@@ -2450,32 +2450,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>47645; 77454</t>
+          <t>47184; 78455</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>83475; 141676</t>
+          <t>92163; 144233</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>110010; 160910</t>
+          <t>108863; 155830</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>114398; 170710</t>
+          <t>135152; 181297</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>167506; 223618</t>
+          <t>164728; 223541</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>220482; 297091</t>
+          <t>240328; 309782</t>
         </is>
       </c>
     </row>
